--- a/generated/spreadsheet/lawful-development-certificate-ldc.xlsx
+++ b/generated/spreadsheet/lawful-development-certificate-ldc.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -568,14 +568,14 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Application sub type</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Further classification of the application type for specific variations within the main application type</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -599,19 +599,19 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Submission date</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>Date the application is submitted in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -630,19 +630,19 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Modules[]</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>List of required modules for this application that can be used to validate the application</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -661,14 +661,18 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
+          <t>Documents[]</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -697,13 +701,13 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -732,13 +736,13 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -748,7 +752,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -767,23 +771,23 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -802,18 +806,18 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Uploaded date</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -837,23 +841,27 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Base64</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -877,12 +885,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Base64</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -892,7 +900,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -916,12 +924,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -931,7 +939,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -955,17 +963,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>File size</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -984,22 +992,18 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
+          <t>Fee</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>File size</t>
-        </is>
-      </c>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1009,7 +1013,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1028,13 +1032,13 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1063,48 +1067,48 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Transactions[]</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="n"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Fee</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Transactions[]</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1114,32 +1118,28 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1163,14 +1163,18 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1180,7 +1184,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1199,18 +1203,18 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1220,51 +1224,47 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n"/>
-      <c r="B23" s="2" t="n"/>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>agent</t>
@@ -1272,14 +1272,18 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1289,7 +1293,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1308,13 +1312,13 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1324,7 +1328,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1343,13 +1347,13 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1378,13 +1382,13 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1413,13 +1417,13 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1429,7 +1433,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1443,18 +1447,14 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1478,19 +1478,19 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>User role</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1500,58 +1500,58 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n"/>
-      <c r="B31" s="2" t="n"/>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Telephone number and email address of the applicant.</t>
+        </is>
+      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>User role</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Telephone number and email address of the applicant.</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1575,14 +1575,18 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1592,7 +1596,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1611,18 +1615,18 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -1632,51 +1636,47 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n"/>
-      <c r="B35" s="2" t="n"/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>Applicants[]</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information for the parties making the application.</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Applicants[]</t>
@@ -1684,14 +1684,18 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1701,7 +1705,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1720,13 +1724,13 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1736,7 +1740,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1755,13 +1759,13 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1790,13 +1794,13 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -1825,13 +1829,13 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -1841,59 +1845,51 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="2" t="n"/>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+        </is>
+      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Conflict to declare</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>Conflict person name</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
@@ -1901,17 +1897,17 @@
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1916,7 @@
       <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Conflict person name</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
@@ -1928,7 +1924,7 @@
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -1943,11 +1939,19 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n"/>
-      <c r="B44" s="2" t="n"/>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+        </is>
+      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
@@ -1955,7 +1959,7 @@
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -1965,24 +1969,24 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Checklist</t>
+          <t>Declaration</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
@@ -1990,7 +1994,7 @@
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>A name of a person</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2005,19 +2009,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="n"/>
+      <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
@@ -2025,12 +2021,12 @@
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2044,7 +2040,7 @@
       <c r="B47" s="2" t="n"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
@@ -2052,12 +2048,12 @@
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2067,11 +2063,19 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n"/>
-      <c r="B48" s="2" t="n"/>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Interest details</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Names and contact details for all parties with an interest in the proposed develpoment.</t>
+        </is>
+      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Applicant interest</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -2079,7 +2083,7 @@
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Description of the applicant's interest in the land</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2094,27 +2098,27 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>Interest details</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>Names and contact details for all parties with an interest in the proposed develpoment.</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="n"/>
+      <c r="B49" s="2" t="n"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Applicant interest</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr"/>
-      <c r="E49" s="2" t="inlineStr"/>
+          <t>Owner details[]</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Description of the applicant's interest in the land</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2124,7 +2128,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2143,13 +2147,13 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2159,7 +2163,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2178,13 +2182,13 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2213,13 +2217,13 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2248,13 +2252,13 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2264,7 +2268,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2278,28 +2282,24 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Informed of application</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Whether the owner has been informed of the application</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2308,29 +2308,33 @@
       <c r="B55" s="2" t="n"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Owner details[]</t>
+          <t>Interested persons[]</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Informed of application</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Whether the owner has been informed of the application</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2349,13 +2353,13 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2365,7 +2369,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2384,13 +2388,13 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -2419,13 +2423,13 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2454,13 +2458,13 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -2470,7 +2474,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2484,18 +2488,14 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Nature of interest</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Description of the nature of a person's interest in the property</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2519,19 +2519,19 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Nature of interest</t>
+          <t>Informed of application</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Description of the nature of a person's interest in the property</t>
+          <t>Whether the person has been informed of the application</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -2550,72 +2550,68 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Informed of application</t>
+          <t>Reason not informed</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Whether the person has been informed of the application</t>
+          <t>Reason why a person was not informed of the application</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n"/>
-      <c r="B63" s="2" t="n"/>
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Details of pre-application advice previously received from the planning authority</t>
+        </is>
+      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Interested persons[]</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>Reason not informed</t>
-        </is>
-      </c>
+          <t>Pre-application advice sought</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr"/>
       <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Reason why a person was not informed of the application</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="n"/>
+      <c r="B64" s="2" t="n"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr"/>
@@ -2623,17 +2619,17 @@
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2638,7 @@
       <c r="B65" s="2" t="n"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
@@ -2650,7 +2646,7 @@
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -2669,7 +2665,7 @@
       <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
@@ -2677,7 +2673,7 @@
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -2696,7 +2692,7 @@
       <c r="B67" s="2" t="n"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
@@ -2704,7 +2700,7 @@
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -2719,24 +2715,36 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n"/>
-      <c r="B68" s="2" t="n"/>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Site boundary</t>
+        </is>
+      </c>
       <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -2746,16 +2754,8 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>Where the proposed development will be built.</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="n"/>
+      <c r="B69" s="2" t="n"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Site locations[]</t>
@@ -2763,19 +2763,19 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -2794,14 +2794,14 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -2825,19 +2825,19 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -2856,14 +2856,14 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -2887,14 +2887,14 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -2918,14 +2918,14 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -2980,14 +2980,14 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>UPRNs[]</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr"/>
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -3002,50 +3002,46 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n"/>
-      <c r="B77" s="2" t="n"/>
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>UPRNs[]</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr"/>
       <c r="E77" s="2" t="inlineStr"/>
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="n"/>
+      <c r="B78" s="2" t="n"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr"/>
@@ -3053,12 +3049,12 @@
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -3072,7 +3068,7 @@
       <c r="B79" s="2" t="n"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Contact reference</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr"/>
@@ -3080,17 +3076,17 @@
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3099,15 +3095,19 @@
       <c r="B80" s="2" t="n"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="E80" s="2" t="inlineStr"/>
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3131,14 +3131,14 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr"/>
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -3162,14 +3162,14 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr"/>
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -3178,37 +3178,6 @@
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="n"/>
-      <c r="B83" s="2" t="n"/>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr"/>
-      <c r="F83" s="2" t="inlineStr"/>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -3216,30 +3185,30 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A49:A63"/>
-    <mergeCell ref="A24:A31"/>
-    <mergeCell ref="A2:A19"/>
-    <mergeCell ref="B64:B68"/>
-    <mergeCell ref="A36:A41"/>
-    <mergeCell ref="B69:B77"/>
-    <mergeCell ref="B45"/>
-    <mergeCell ref="A78:A83"/>
-    <mergeCell ref="A64:A68"/>
-    <mergeCell ref="A45"/>
-    <mergeCell ref="A32:A35"/>
-    <mergeCell ref="B49:B63"/>
-    <mergeCell ref="B78:B83"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B36:B41"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="A69:A77"/>
-    <mergeCell ref="B2:B19"/>
-    <mergeCell ref="B24:B31"/>
-    <mergeCell ref="A46:A48"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="B35:B40"/>
+    <mergeCell ref="A48:A62"/>
+    <mergeCell ref="B31:B34"/>
+    <mergeCell ref="A77:A82"/>
+    <mergeCell ref="A44"/>
+    <mergeCell ref="A63:A67"/>
+    <mergeCell ref="B2:B18"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="B48:B62"/>
+    <mergeCell ref="B63:B67"/>
+    <mergeCell ref="B77:B82"/>
+    <mergeCell ref="B68:B76"/>
+    <mergeCell ref="B41:B43"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="B23:B30"/>
+    <mergeCell ref="A45:A47"/>
+    <mergeCell ref="A2:A18"/>
+    <mergeCell ref="A68:A76"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="A35:A40"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="B44"/>
+    <mergeCell ref="A23:A30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/lawful-development-certificate-ldc.xlsx
+++ b/generated/spreadsheet/lawful-development-certificate-ldc.xlsx
@@ -2053,7 +2053,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">

--- a/generated/spreadsheet/lawful-development-certificate-ldc.xlsx
+++ b/generated/spreadsheet/lawful-development-certificate-ldc.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="72" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -491,29 +491,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Submission reference</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>A unique reference for the submission</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -532,7 +532,7 @@
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -563,19 +563,19 @@
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Specification profile</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>The specification profile used to determine context-specific allowed codelist values for the application</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -594,24 +594,24 @@
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -625,24 +625,24 @@
       <c r="B6" s="2" t="n"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
+          <t>Submitted at</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>The date and time the application was submitted</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -656,28 +656,24 @@
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Created at</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The date and time the submission payload was created</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -691,7 +687,7 @@
       <c r="B8" s="2" t="n"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -701,13 +697,13 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -726,7 +722,7 @@
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -736,13 +732,13 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -752,7 +748,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -761,7 +757,7 @@
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -771,23 +767,23 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -796,7 +792,7 @@
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -806,18 +802,18 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -831,7 +827,7 @@
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -841,27 +837,23 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Base64</t>
-        </is>
-      </c>
+          <t>Uploaded date</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -870,7 +862,7 @@
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -885,12 +877,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>Base64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -900,7 +892,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -909,7 +901,7 @@
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -924,12 +916,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -939,7 +931,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -948,7 +940,7 @@
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -963,17 +955,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>File size</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -987,33 +979,37 @@
       <c r="B16" s="2" t="n"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Fee</t>
+          <t>Documents[]</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>File size</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1018,7 @@
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1032,18 +1028,18 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1057,7 +1053,7 @@
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1067,48 +1063,48 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Transactions[]</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr"/>
-      <c r="E19" s="2" t="inlineStr"/>
+          <t>Submission details</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Fee</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Transactions[]</t>
+        </is>
+      </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1118,28 +1114,32 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="n"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1163,18 +1163,14 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1184,7 +1180,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1203,18 +1199,18 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1224,47 +1220,51 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n"/>
-      <c r="B24" s="2" t="n"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>agent</t>
@@ -1272,18 +1272,14 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1293,7 +1289,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1312,13 +1308,13 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1328,7 +1324,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1347,13 +1343,13 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1382,13 +1378,13 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1417,13 +1413,13 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1433,7 +1429,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1447,14 +1443,18 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1478,19 +1478,19 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1500,58 +1500,58 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Telephone number and email address of the applicant.</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="2" t="n"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n"/>
-      <c r="B32" s="2" t="n"/>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Telephone number and email address of the applicant.</t>
+        </is>
+      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1575,18 +1575,14 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1596,7 +1592,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1615,18 +1611,18 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -1636,47 +1632,51 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information for the parties making the application.</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="n"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n"/>
-      <c r="B36" s="2" t="n"/>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Applicants[]</t>
@@ -1684,18 +1684,14 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1705,7 +1701,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1724,13 +1720,13 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1740,7 +1736,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1759,13 +1755,13 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1794,13 +1790,13 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -1829,13 +1825,13 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -1845,51 +1841,59 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="2" t="n"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr"/>
-      <c r="E41" s="2" t="inlineStr"/>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n"/>
-      <c r="B42" s="2" t="n"/>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+        </is>
+      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Conflict person name</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
@@ -1897,17 +1901,17 @@
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1920,7 @@
       <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
@@ -1924,7 +1928,7 @@
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Reference to the applicant or agent with the conflict</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -1939,19 +1943,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="n"/>
+      <c r="B44" s="2" t="n"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
@@ -1959,7 +1955,7 @@
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -1969,24 +1965,24 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Declaration</t>
+          <t>Checklist</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
@@ -1994,7 +1990,7 @@
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2009,11 +2005,19 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n"/>
-      <c r="B46" s="2" t="n"/>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Signed and dated verification of the application's accuracy.</t>
+        </is>
+      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
@@ -2021,12 +2025,12 @@
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2040,7 +2044,7 @@
       <c r="B47" s="2" t="n"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
@@ -2048,12 +2052,12 @@
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2063,19 +2067,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Interest details</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Names and contact details for all parties with an interest in the proposed develpoment.</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="2" t="n"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Applicant interest</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -2083,12 +2079,12 @@
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Description of the applicant's interest in the land</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2098,37 +2094,37 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n"/>
-      <c r="B49" s="2" t="n"/>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Interest details</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Names and contact details for all parties with an interest in the proposed develpoment.</t>
+        </is>
+      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Owner details[]</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Applicant interest type</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr"/>
+      <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The applicant’s relationship to the land, property or building</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2147,13 +2143,13 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2163,7 +2159,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2182,13 +2178,13 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2217,13 +2213,13 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2252,13 +2248,13 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2268,7 +2264,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2282,24 +2278,28 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Informed of application</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Whether the owner has been informed of the application</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2308,33 +2308,29 @@
       <c r="B55" s="2" t="n"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Interested persons[]</t>
+          <t>Owner details[]</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Informed of application</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>Whether the owner has been informed of the application</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2353,13 +2349,13 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2369,7 +2365,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2388,13 +2384,13 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -2423,13 +2419,13 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2458,13 +2454,13 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -2474,7 +2470,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2488,14 +2484,18 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Nature of interest</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Description of the nature of a person's interest in the property</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2519,19 +2519,19 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Informed of application</t>
+          <t>Nature of interest</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Whether the person has been informed of the application</t>
+          <t>Description of the nature of a person's interest in the property</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -2550,68 +2550,72 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Reason not informed</t>
+          <t>Informed of application</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Reason why a person was not informed of the application</t>
+          <t>Whether the person has been informed of the application</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="n"/>
+      <c r="B63" s="2" t="n"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr"/>
+          <t>Interested persons[]</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Reason not informed</t>
+        </is>
+      </c>
       <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Reason why a person was not informed of the application</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n"/>
-      <c r="B64" s="2" t="n"/>
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Details of pre-application advice previously received from the planning authority</t>
+        </is>
+      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr"/>
@@ -2619,17 +2623,17 @@
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2642,7 @@
       <c r="B65" s="2" t="n"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
@@ -2646,7 +2650,7 @@
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -2665,7 +2669,7 @@
       <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
@@ -2673,12 +2677,12 @@
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -2692,7 +2696,7 @@
       <c r="B67" s="2" t="n"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
@@ -2700,12 +2704,12 @@
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -2715,36 +2719,24 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>Where the proposed development will be built.</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="n"/>
+      <c r="B68" s="2" t="n"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>Site boundary</t>
-        </is>
-      </c>
+          <t>Advice summary</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr"/>
       <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -2754,8 +2746,16 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n"/>
-      <c r="B69" s="2" t="n"/>
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Site locations[]</t>
@@ -2763,19 +2763,19 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -2794,14 +2794,14 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -2825,19 +2825,19 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -2856,19 +2856,19 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -2887,19 +2887,19 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -2918,19 +2918,19 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -2980,14 +2980,14 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr"/>
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>A text description providing details about the subject.</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -3002,46 +3002,50 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="n"/>
+      <c r="B77" s="2" t="n"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="E77" s="2" t="inlineStr"/>
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n"/>
-      <c r="B78" s="2" t="n"/>
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Site seen from public area</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr"/>
@@ -3049,12 +3053,12 @@
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -3068,7 +3072,7 @@
       <c r="B79" s="2" t="n"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr"/>
@@ -3076,17 +3080,17 @@
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3095,19 +3099,15 @@
       <c r="B80" s="2" t="n"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>Full name</t>
-        </is>
-      </c>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr"/>
       <c r="E80" s="2" t="inlineStr"/>
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3131,14 +3131,14 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Full name</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr"/>
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -3162,22 +3162,53 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr"/>
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
+          <t>A phone number</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n"/>
+      <c r="B83" s="2" t="n"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr"/>
+      <c r="F83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
           <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -3185,30 +3216,30 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B35:B40"/>
-    <mergeCell ref="A48:A62"/>
-    <mergeCell ref="B31:B34"/>
-    <mergeCell ref="A77:A82"/>
-    <mergeCell ref="A44"/>
-    <mergeCell ref="A63:A67"/>
-    <mergeCell ref="B2:B18"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="B48:B62"/>
-    <mergeCell ref="B63:B67"/>
-    <mergeCell ref="B77:B82"/>
-    <mergeCell ref="B68:B76"/>
-    <mergeCell ref="B41:B43"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="B23:B30"/>
-    <mergeCell ref="A45:A47"/>
-    <mergeCell ref="A2:A18"/>
-    <mergeCell ref="A68:A76"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="A35:A40"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="B44"/>
-    <mergeCell ref="A23:A30"/>
+    <mergeCell ref="A49:A63"/>
+    <mergeCell ref="A24:A31"/>
+    <mergeCell ref="A2:A19"/>
+    <mergeCell ref="B64:B68"/>
+    <mergeCell ref="A36:A41"/>
+    <mergeCell ref="B69:B77"/>
+    <mergeCell ref="B45"/>
+    <mergeCell ref="A78:A83"/>
+    <mergeCell ref="A64:A68"/>
+    <mergeCell ref="A45"/>
+    <mergeCell ref="A32:A35"/>
+    <mergeCell ref="B49:B63"/>
+    <mergeCell ref="B78:B83"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B36:B41"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="A69:A77"/>
+    <mergeCell ref="B2:B19"/>
+    <mergeCell ref="B24:B31"/>
+    <mergeCell ref="A46:A48"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="B32:B35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/lawful-development-certificate-ldc.xlsx
+++ b/generated/spreadsheet/lawful-development-certificate-ldc.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -435,9 +435,9 @@
     <col width="31" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="72" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -1413,13 +1413,17 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>Address Text</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1448,13 +1452,17 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1478,14 +1486,22 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1509,19 +1525,19 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -1531,58 +1547,58 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Telephone number and email address of the applicant.</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n"/>
-      <c r="B33" s="2" t="n"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Telephone number and email address of the applicant.</t>
+        </is>
+      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1606,18 +1622,14 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1627,7 +1639,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1646,18 +1658,18 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -1667,47 +1679,51 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information for the parties making the application.</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n"/>
-      <c r="B37" s="2" t="n"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Applicants[]</t>
@@ -1715,18 +1731,14 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1736,7 +1748,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1755,13 +1767,13 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1771,7 +1783,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1790,13 +1802,13 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -1825,13 +1837,13 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -1860,58 +1872,66 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Text representation of an address or site</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>The postal code</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Conflict to declare</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1920,15 +1940,27 @@
       <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr"/>
-      <c r="E43" s="2" t="inlineStr"/>
-      <c r="F43" s="2" t="inlineStr"/>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Reference to the applicant or agent with the conflict</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -1943,11 +1975,19 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n"/>
-      <c r="B44" s="2" t="n"/>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+        </is>
+      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
@@ -1955,34 +1995,26 @@
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="n"/>
+      <c r="B45" s="2" t="n"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
@@ -1990,7 +2022,7 @@
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>Reference to the applicant or agent with the conflict</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2000,24 +2032,16 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="n"/>
+      <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
@@ -2025,7 +2049,7 @@
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2035,16 +2059,24 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n"/>
-      <c r="B47" s="2" t="n"/>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+        </is>
+      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
@@ -2052,12 +2084,12 @@
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2067,11 +2099,19 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n"/>
-      <c r="B48" s="2" t="n"/>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Signed and dated verification of the application's accuracy.</t>
+        </is>
+      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -2079,12 +2119,12 @@
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2094,19 +2134,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>Interest details</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>Names and contact details for all parties with an interest in the proposed develpoment.</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="n"/>
+      <c r="B49" s="2" t="n"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Applicant interest type</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
@@ -2114,12 +2146,12 @@
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>The applicant’s relationship to the land, property or building</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -2133,63 +2165,55 @@
       <c r="B50" s="2" t="n"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Owner details[]</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Declaration date</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr"/>
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n"/>
-      <c r="B51" s="2" t="n"/>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Interest details</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Names and contact details for all parties with an interest in the proposed develpoment.</t>
+        </is>
+      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Owner details[]</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>First Name</t>
-        </is>
-      </c>
+          <t>Applicant interest type</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="inlineStr"/>
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The applicant’s relationship to the land, property or building</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -2213,13 +2237,13 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2229,7 +2253,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2248,13 +2272,13 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2283,13 +2307,13 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2299,7 +2323,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2313,19 +2337,27 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Informed of application</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr"/>
-      <c r="F55" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Whether the owner has been informed of the application</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -2339,7 +2371,7 @@
       <c r="B56" s="2" t="n"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Interested persons[]</t>
+          <t>Owner details[]</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -2349,13 +2381,17 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr"/>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2374,7 +2410,7 @@
       <c r="B57" s="2" t="n"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Interested persons[]</t>
+          <t>Owner details[]</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2384,13 +2420,17 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr"/>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -2400,7 +2440,7 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2409,28 +2449,24 @@
       <c r="B58" s="2" t="n"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Interested persons[]</t>
+          <t>Owner details[]</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>Last Name</t>
-        </is>
-      </c>
+          <t>Informed of application</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Whether the owner has been informed of the application</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -2454,13 +2490,13 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -2470,7 +2506,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2489,13 +2525,13 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -2505,7 +2541,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2519,14 +2555,18 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Nature of interest</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Last Name</t>
+        </is>
+      </c>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Description of the nature of a person's interest in the property</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -2550,19 +2590,27 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Informed of application</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr"/>
-      <c r="F62" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Whether the person has been informed of the application</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -2581,14 +2629,22 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Reason not informed</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr"/>
-      <c r="F63" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Reason why a person was not informed of the application</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -2603,37 +2659,41 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="n"/>
+      <c r="B64" s="2" t="n"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr"/>
-      <c r="E64" s="2" t="inlineStr"/>
-      <c r="F64" s="2" t="inlineStr"/>
+          <t>Interested persons[]</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2642,15 +2702,19 @@
       <c r="B65" s="2" t="n"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr"/>
+          <t>Interested persons[]</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Nature of interest</t>
+        </is>
+      </c>
       <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>Description of the nature of a person's interest in the property</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -2660,7 +2724,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2669,25 +2733,29 @@
       <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr"/>
+          <t>Interested persons[]</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Informed of application</t>
+        </is>
+      </c>
       <c r="E66" s="2" t="inlineStr"/>
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Whether the person has been informed of the application</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2696,20 +2764,24 @@
       <c r="B67" s="2" t="n"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr"/>
+          <t>Interested persons[]</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Reason not informed</t>
+        </is>
+      </c>
       <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Reason why a person was not informed of the application</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -2719,11 +2791,19 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n"/>
-      <c r="B68" s="2" t="n"/>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Details of pre-application advice previously received from the planning authority</t>
+        </is>
+      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
@@ -2731,51 +2811,39 @@
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>Where the proposed development will be built.</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="n"/>
+      <c r="B69" s="2" t="n"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>Site boundary</t>
-        </is>
-      </c>
+          <t>Officer name</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr"/>
       <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -2789,19 +2857,15 @@
       <c r="B70" s="2" t="n"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>Address Text</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr"/>
       <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -2820,24 +2884,20 @@
       <c r="B71" s="2" t="n"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Advice date</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr"/>
       <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -2851,24 +2911,20 @@
       <c r="B72" s="2" t="n"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>Easting</t>
-        </is>
-      </c>
+          <t>Advice summary</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr"/>
       <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -2878,8 +2934,16 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n"/>
-      <c r="B73" s="2" t="n"/>
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>Site locations[]</t>
@@ -2887,24 +2951,24 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>A polygon or multipolygon boundary</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>multipolygon</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2918,24 +2982,28 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2949,19 +3017,23 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -2980,14 +3052,18 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject.</t>
+          <t>Unique Property Reference Numbers (UPRNs) for existing premises within a site boundary</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -3011,14 +3087,18 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>USRNs[]</t>
+        </is>
+      </c>
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Unique Street Reference Numbers (USRNs) associated with the site</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -3033,37 +3113,33 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="n"/>
+      <c r="B78" s="2" t="n"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Easting</t>
+        </is>
+      </c>
       <c r="E78" s="2" t="inlineStr"/>
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3072,25 +3148,29 @@
       <c r="B79" s="2" t="n"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Northing</t>
+        </is>
+      </c>
       <c r="E79" s="2" t="inlineStr"/>
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3099,20 +3179,24 @@
       <c r="B80" s="2" t="n"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
       <c r="E80" s="2" t="inlineStr"/>
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -3126,55 +3210,59 @@
       <c r="B81" s="2" t="n"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
+          <t>Site locations[]</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr"/>
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n"/>
-      <c r="B82" s="2" t="n"/>
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr"/>
       <c r="E82" s="2" t="inlineStr"/>
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -3188,27 +3276,143 @@
       <c r="B83" s="2" t="n"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Site visit contact type</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr"/>
       <c r="E83" s="2" t="inlineStr"/>
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n"/>
+      <c r="B84" s="2" t="n"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr"/>
+      <c r="E84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n"/>
+      <c r="B85" s="2" t="n"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr"/>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>The complete name of a person</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n"/>
+      <c r="B86" s="2" t="n"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr"/>
+      <c r="F86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>A phone number</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n"/>
+      <c r="B87" s="2" t="n"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr"/>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
           <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -3216,30 +3420,30 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A49:A63"/>
-    <mergeCell ref="A24:A31"/>
+    <mergeCell ref="B73:B81"/>
+    <mergeCell ref="A37:A43"/>
+    <mergeCell ref="A51:A67"/>
     <mergeCell ref="A2:A19"/>
-    <mergeCell ref="B64:B68"/>
-    <mergeCell ref="A36:A41"/>
-    <mergeCell ref="B69:B77"/>
-    <mergeCell ref="B45"/>
-    <mergeCell ref="A78:A83"/>
-    <mergeCell ref="A64:A68"/>
-    <mergeCell ref="A45"/>
-    <mergeCell ref="A32:A35"/>
-    <mergeCell ref="B49:B63"/>
-    <mergeCell ref="B78:B83"/>
+    <mergeCell ref="A82:A87"/>
+    <mergeCell ref="B37:B43"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="A68:A72"/>
+    <mergeCell ref="B68:B72"/>
+    <mergeCell ref="B47"/>
+    <mergeCell ref="B82:B87"/>
+    <mergeCell ref="B24:B32"/>
+    <mergeCell ref="A33:A36"/>
+    <mergeCell ref="A48:A50"/>
     <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B36:B41"/>
+    <mergeCell ref="B33:B36"/>
+    <mergeCell ref="A73:A81"/>
+    <mergeCell ref="A24:A32"/>
+    <mergeCell ref="B48:B50"/>
     <mergeCell ref="B20:B23"/>
-    <mergeCell ref="A69:A77"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="B51:B67"/>
     <mergeCell ref="B2:B19"/>
-    <mergeCell ref="B24:B31"/>
-    <mergeCell ref="A46:A48"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="A47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
